--- a/03-系列教学2(BV1Do5jzJEgn)/R201/data/returndaily.xlsx
+++ b/03-系列教学2(BV1Do5jzJEgn)/R201/data/returndaily.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B61"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -372,6 +372,11 @@
           <t>SH_return_daily</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>SZ_return_daily</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
@@ -380,6 +385,9 @@
       <c r="B2">
         <v>0.0188</v>
       </c>
+      <c r="C2">
+        <v>-0.0248</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2">
@@ -388,6 +396,9 @@
       <c r="B3">
         <v>0.0504</v>
       </c>
+      <c r="C3">
+        <v>-0.0227</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2">
@@ -396,6 +407,9 @@
       <c r="B4">
         <v>-0.0089</v>
       </c>
+      <c r="C4">
+        <v>-0.033</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2">
@@ -404,6 +418,9 @@
       <c r="B5">
         <v>0.0507</v>
       </c>
+      <c r="C5">
+        <v>0.0484</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2">
@@ -412,6 +429,9 @@
       <c r="B6">
         <v>-0.0554</v>
       </c>
+      <c r="C6">
+        <v>0.017</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2">
@@ -420,6 +440,9 @@
       <c r="B7">
         <v>0.019</v>
       </c>
+      <c r="C7">
+        <v>-0.0101</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2">
@@ -428,6 +451,9 @@
       <c r="B8">
         <v>-0.0327</v>
       </c>
+      <c r="C8">
+        <v>0.0046</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2">
@@ -436,6 +462,9 @@
       <c r="B9">
         <v>-0.0201</v>
       </c>
+      <c r="C9">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2">
@@ -444,6 +473,9 @@
       <c r="B10">
         <v>-0.0448</v>
       </c>
+      <c r="C10">
+        <v>0.0411</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2">
@@ -452,6 +484,9 @@
       <c r="B11">
         <v>-0.0011</v>
       </c>
+      <c r="C11">
+        <v>-0.0016</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2">
@@ -460,6 +495,9 @@
       <c r="B12">
         <v>0.0538</v>
       </c>
+      <c r="C12">
+        <v>-0.007900000000000001</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2">
@@ -468,6 +506,9 @@
       <c r="B13">
         <v>-0.0443</v>
       </c>
+      <c r="C13">
+        <v>-0.0036</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2">
@@ -476,6 +517,9 @@
       <c r="B14">
         <v>0.0216</v>
       </c>
+      <c r="C14">
+        <v>0.0176</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2">
@@ -484,6 +528,9 @@
       <c r="B15">
         <v>-0.043</v>
       </c>
+      <c r="C15">
+        <v>0.0048</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2">
@@ -492,6 +539,9 @@
       <c r="B16">
         <v>0.0034</v>
       </c>
+      <c r="C16">
+        <v>-0.0307</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2">
@@ -500,6 +550,9 @@
       <c r="B17">
         <v>-0.0019</v>
       </c>
+      <c r="C17">
+        <v>-0.0016</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2">
@@ -508,6 +561,9 @@
       <c r="B18">
         <v>0.0215</v>
       </c>
+      <c r="C18">
+        <v>-0.0196</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2">
@@ -516,6 +572,9 @@
       <c r="B19">
         <v>0.0086</v>
       </c>
+      <c r="C19">
+        <v>-0.0736</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2">
@@ -524,6 +583,9 @@
       <c r="B20">
         <v>-0.0146</v>
       </c>
+      <c r="C20">
+        <v>-0.0157</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2">
@@ -532,6 +594,9 @@
       <c r="B21">
         <v>0.0197</v>
       </c>
+      <c r="C21">
+        <v>-0.0138</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2">
@@ -540,6 +605,9 @@
       <c r="B22">
         <v>-0.0173</v>
       </c>
+      <c r="C22">
+        <v>0.0372</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2">
@@ -548,6 +616,9 @@
       <c r="B23">
         <v>-0.0296</v>
       </c>
+      <c r="C23">
+        <v>0.0222</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2">
@@ -556,6 +627,9 @@
       <c r="B24">
         <v>0.0317</v>
       </c>
+      <c r="C24">
+        <v>-0.008200000000000001</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2">
@@ -564,6 +638,9 @@
       <c r="B25">
         <v>-0.0078</v>
       </c>
+      <c r="C25">
+        <v>-0.0321</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2">
@@ -572,6 +649,9 @@
       <c r="B26">
         <v>0.0008</v>
       </c>
+      <c r="C26">
+        <v>-0.0004</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2">
@@ -580,6 +660,9 @@
       <c r="B27">
         <v>-0.0371</v>
       </c>
+      <c r="C27">
+        <v>0.0251</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2">
@@ -588,6 +671,9 @@
       <c r="B28">
         <v>-0.0282</v>
       </c>
+      <c r="C28">
+        <v>0.0101</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2">
@@ -596,6 +682,9 @@
       <c r="B29">
         <v>-0.0441</v>
       </c>
+      <c r="C29">
+        <v>0.0358</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2">
@@ -604,6 +693,9 @@
       <c r="B30">
         <v>-0.0266</v>
       </c>
+      <c r="C30">
+        <v>0.0034</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2">
@@ -612,6 +704,9 @@
       <c r="B31">
         <v>-0.0336</v>
       </c>
+      <c r="C31">
+        <v>-0.0335</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2">
@@ -620,6 +715,9 @@
       <c r="B32">
         <v>0.0189</v>
       </c>
+      <c r="C32">
+        <v>-0.0122</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2">
@@ -628,6 +726,9 @@
       <c r="B33">
         <v>-0.016</v>
       </c>
+      <c r="C33">
+        <v>-0.0225</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2">
@@ -636,6 +737,9 @@
       <c r="B34">
         <v>0.0358</v>
       </c>
+      <c r="C34">
+        <v>0.008</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2">
@@ -644,6 +748,9 @@
       <c r="B35">
         <v>-0.0156</v>
       </c>
+      <c r="C35">
+        <v>0.007900000000000001</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2">
@@ -652,6 +759,9 @@
       <c r="B36">
         <v>0.0057</v>
       </c>
+      <c r="C36">
+        <v>-0.026</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2">
@@ -660,6 +770,9 @@
       <c r="B37">
         <v>0.0066</v>
       </c>
+      <c r="C37">
+        <v>0.009599999999999999</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2">
@@ -668,6 +781,9 @@
       <c r="B38">
         <v>0.0107</v>
       </c>
+      <c r="C38">
+        <v>0.0199</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2">
@@ -676,6 +792,9 @@
       <c r="B39">
         <v>-0.0371</v>
       </c>
+      <c r="C39">
+        <v>-0.0138</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2">
@@ -684,6 +803,9 @@
       <c r="B40">
         <v>0.0045</v>
       </c>
+      <c r="C40">
+        <v>0.0044</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2">
@@ -692,6 +814,9 @@
       <c r="B41">
         <v>0.0515</v>
       </c>
+      <c r="C41">
+        <v>0.0011</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2">
@@ -700,6 +825,9 @@
       <c r="B42">
         <v>0.0181</v>
       </c>
+      <c r="C42">
+        <v>-0.0237</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2">
@@ -708,6 +836,9 @@
       <c r="B43">
         <v>-0.0122</v>
       </c>
+      <c r="C43">
+        <v>-0.0454</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2">
@@ -716,6 +847,9 @@
       <c r="B44">
         <v>-0.0121</v>
       </c>
+      <c r="C44">
+        <v>0.0496</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2">
@@ -724,6 +858,9 @@
       <c r="B45">
         <v>0.0461</v>
       </c>
+      <c r="C45">
+        <v>0.0204</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2">
@@ -732,6 +869,9 @@
       <c r="B46">
         <v>0.0129</v>
       </c>
+      <c r="C46">
+        <v>-0.025</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2">
@@ -740,6 +880,9 @@
       <c r="B47">
         <v>-0.0279</v>
       </c>
+      <c r="C47">
+        <v>0.014</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2">
@@ -748,6 +891,9 @@
       <c r="B48">
         <v>-0.0078</v>
       </c>
+      <c r="C48">
+        <v>-0.0195</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2">
@@ -756,6 +902,9 @@
       <c r="B49">
         <v>0.0023</v>
       </c>
+      <c r="C49">
+        <v>0.017</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2">
@@ -764,6 +913,9 @@
       <c r="B50">
         <v>0.0161</v>
       </c>
+      <c r="C50">
+        <v>-0.0263</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2">
@@ -772,6 +924,9 @@
       <c r="B51">
         <v>0.0094</v>
       </c>
+      <c r="C51">
+        <v>-0.0176</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2">
@@ -780,6 +935,9 @@
       <c r="B52">
         <v>0.0049</v>
       </c>
+      <c r="C52">
+        <v>-0.0238</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2">
@@ -788,6 +946,9 @@
       <c r="B53">
         <v>0.0295</v>
       </c>
+      <c r="C53">
+        <v>-0.0047</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2">
@@ -796,6 +957,9 @@
       <c r="B54">
         <v>-0.0175</v>
       </c>
+      <c r="C54">
+        <v>0.0308</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2">
@@ -804,6 +968,9 @@
       <c r="B55">
         <v>-0.0152</v>
       </c>
+      <c r="C55">
+        <v>-0.0339</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2">
@@ -812,6 +979,9 @@
       <c r="B56">
         <v>-0.0126</v>
       </c>
+      <c r="C56">
+        <v>-0.0078</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2">
@@ -820,6 +990,9 @@
       <c r="B57">
         <v>-0.0205</v>
       </c>
+      <c r="C57">
+        <v>0.0268</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2">
@@ -828,6 +1001,9 @@
       <c r="B58">
         <v>-0.0059</v>
       </c>
+      <c r="C58">
+        <v>-0.0422</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2">
@@ -836,6 +1012,9 @@
       <c r="B59">
         <v>-0.0192</v>
       </c>
+      <c r="C59">
+        <v>-0.0112</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2">
@@ -844,6 +1023,9 @@
       <c r="B60">
         <v>0.018</v>
       </c>
+      <c r="C60">
+        <v>-0.0054</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2">
@@ -851,6 +1033,9 @@
       </c>
       <c r="B61">
         <v>0.032</v>
+      </c>
+      <c r="C61">
+        <v>-0.0513</v>
       </c>
     </row>
   </sheetData>
